--- a/backend/files/templates/template_pr.xlsx
+++ b/backend/files/templates/template_pr.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
   <si>
     <t>MESABI METALLICS COMPANY LLC</t>
   </si>
@@ -91,19 +91,10 @@
     <t>Indentor:</t>
   </si>
   <si>
-    <t>Erin Nordstrand</t>
-  </si>
-  <si>
     <t>Verified by :</t>
   </si>
   <si>
-    <t>Shane Holman</t>
-  </si>
-  <si>
     <t>Approved by</t>
-  </si>
-  <si>
-    <t>Joe Broking</t>
   </si>
   <si>
     <t>Project Head</t>
@@ -2516,25 +2507,19 @@
       <c r="A21" t="s" s="55">
         <v>25</v>
       </c>
-      <c r="B21" t="s" s="56">
+      <c r="B21" s="56"/>
+      <c r="C21" t="s" s="57">
         <v>26</v>
       </c>
-      <c r="C21" t="s" s="57">
-        <v>27</v>
-      </c>
-      <c r="D21" t="s" s="57">
-        <v>28</v>
-      </c>
+      <c r="D21" s="57"/>
       <c r="E21" s="58"/>
       <c r="F21" s="59"/>
       <c r="G21" s="58"/>
       <c r="H21" s="59"/>
       <c r="I21" t="s" s="60">
-        <v>29</v>
-      </c>
-      <c r="J21" t="s" s="61">
-        <v>30</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J21" s="61"/>
       <c r="K21" s="47"/>
       <c r="L21" s="48"/>
     </row>
@@ -2548,7 +2533,7 @@
       <c r="G22" s="65"/>
       <c r="H22" s="66"/>
       <c r="I22" t="s" s="60">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
@@ -2598,7 +2583,7 @@
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="s" s="76">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B26" s="44"/>
       <c r="C26" s="45"/>
@@ -2614,7 +2599,7 @@
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="s" s="76">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B27" s="44"/>
       <c r="C27" s="45"/>
@@ -2630,7 +2615,7 @@
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="s" s="76">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B28" s="44"/>
       <c r="C28" s="45"/>
@@ -2646,7 +2631,7 @@
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="s" s="76">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B29" s="44"/>
       <c r="C29" s="45"/>
